--- a/Result/profitability/4530.xlsx
+++ b/Result/profitability/4530.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.36</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.10125</v>
+        <v>-0.105</v>
       </c>
       <c r="N2" t="n">
-        <v>31.055</v>
+        <v>25.67125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.10375</v>
+        <v>-0.07625000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>26.76375</v>
+        <v>22.59625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0675</v>
+        <v>-0.10375</v>
       </c>
       <c r="N4" t="n">
-        <v>23.605</v>
+        <v>19.53</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1025</v>
+        <v>-0.14</v>
       </c>
       <c r="N5" t="n">
-        <v>20.7825</v>
+        <v>15.6975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08624999999999999</v>
+        <v>-0.12625</v>
       </c>
       <c r="N6" t="n">
-        <v>16.83625</v>
+        <v>13.07125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1175</v>
+        <v>-0.28125</v>
       </c>
       <c r="N7" t="n">
-        <v>13.775</v>
+        <v>6.86</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.29</v>
+        <v>-0.3125</v>
       </c>
       <c r="N8" t="n">
-        <v>7.568750000000001</v>
+        <v>4.10375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>-1.11</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.40375</v>
+        <v>-0.4037500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>5.08375</v>
+        <v>5.083749999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>-0.27</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3925</v>
+        <v>-0.3925000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9675</v>
+        <v>4.967499999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.415</v>
       </c>
       <c r="N11" t="n">
-        <v>3.220000000000001</v>
+        <v>3.22</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.5437500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1450000000000005</v>
+        <v>0.145</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4530</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>103</v>
+      </c>
+      <c r="D75" t="n">
+        <v>107</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-22.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.10375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.73625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-27.72</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.126829268292683</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-40.68</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.083067092651757</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
